--- a/gworkspace-webapps/SimpleBMN/Template_Spreadsheet_BMN.xlsx
+++ b/gworkspace-webapps/SimpleBMN/Template_Spreadsheet_BMN.xlsx
@@ -1,38 +1,44 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10913"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <workbookPr codeName="ThisWorkbook"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/baizan/Developer/projects/tools/HelpfullScript/gworkspace-webapps/SimpleBMN/"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{96052C5D-9A87-8748-A0B0-DB89BD663EFA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
-  <bookViews>
-    <workbookView xWindow="0" yWindow="600" windowWidth="33600" windowHeight="18980" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
-  </bookViews>
   <sheets>
     <sheet name="Usulan-PP" sheetId="1" r:id="rId1"/>
     <sheet name="BA-PP" sheetId="2" r:id="rId2"/>
     <sheet name="L-PP-AC" sheetId="3" r:id="rId3"/>
+    <sheet name="LKH-ISP" sheetId="4" r:id="rId4"/>
   </sheets>
-  <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1">'BA-PP'!A1:AB1</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2">'L-PP-AC'!A1:AF1</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0">'Usulan-PP'!A1:Z1</definedName>
-  </definedNames>
-  <calcPr calcId="0"/>
 </workbook>
 </file>
 
-<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
+<file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
+<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xlrd="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
+  <metadataTypes count="1">
+    <metadataType name="XLDAPR" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1" cellMeta="1"/>
+  </metadataTypes>
+  <futureMetadata name="XLDAPR" count="1">
+    <bk>
+      <extLst>
+        <ext uri="{bdbb8cdc-fa1e-496e-a857-3c3f30c029c3}">
+          <xda:dynamicArrayProperties fDynamic="1" fCollapsed="0"/>
+        </ext>
+      </extLst>
+    </bk>
+  </futureMetadata>
+  <cellMetadata count="1">
+    <bk>
+      <rc t="1" v="0"/>
+    </bk>
+  </cellMetadata>
+</metadata>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:vt="http://schemas.openxmlformats.org/officeDocument/2006/docPropsVTypes">
+  <numFmts count="1">
+    <numFmt numFmtId="56" formatCode="&quot;上午/下午 &quot;hh&quot;時&quot;mm&quot;分&quot;ss&quot;秒 &quot;"/>
+  </numFmts>
+  <fonts count="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -62,21 +68,13 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleMedium4"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
-  </extLst>
 </styleSheet>
 </file>
 
@@ -401,105 +399,41 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
-  <cols>
-    <col min="1" max="1" width="12.83203125" customWidth="1"/>
-    <col min="2" max="2" width="13.83203125" customWidth="1"/>
-    <col min="3" max="3" width="16.83203125" customWidth="1"/>
-    <col min="4" max="5" width="15.83203125" customWidth="1"/>
-    <col min="6" max="7" width="12.83203125" customWidth="1"/>
-    <col min="8" max="9" width="13.83203125" customWidth="1"/>
-    <col min="10" max="11" width="12.83203125" customWidth="1"/>
-    <col min="12" max="12" width="15.83203125" customWidth="1"/>
-    <col min="13" max="15" width="12.83203125" customWidth="1"/>
-    <col min="16" max="16" width="15.83203125" customWidth="1"/>
-    <col min="17" max="17" width="17.83203125" customWidth="1"/>
-    <col min="18" max="18" width="21.83203125" customWidth="1"/>
-    <col min="19" max="19" width="23.83203125" customWidth="1"/>
-    <col min="20" max="20" width="21.83203125" customWidth="1"/>
-    <col min="21" max="22" width="27.83203125" customWidth="1"/>
-    <col min="23" max="23" width="15.83203125" customWidth="1"/>
-    <col min="24" max="24" width="14.83203125" customWidth="1"/>
-    <col min="25" max="26" width="12.83203125" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="30" customHeight="1" x14ac:dyDescent="0.2"/>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <sheetData/>
+  <ignoredErrors>
+    <ignoredError numberStoredAsText="1" sqref="A1"/>
+  </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
-  <cols>
-    <col min="1" max="2" width="12.83203125" customWidth="1"/>
-    <col min="3" max="3" width="16.83203125" customWidth="1"/>
-    <col min="4" max="4" width="12.83203125" customWidth="1"/>
-    <col min="5" max="5" width="17.83203125" customWidth="1"/>
-    <col min="6" max="6" width="13.83203125" customWidth="1"/>
-    <col min="7" max="10" width="12.83203125" customWidth="1"/>
-    <col min="11" max="11" width="20.83203125" customWidth="1"/>
-    <col min="12" max="12" width="12.83203125" customWidth="1"/>
-    <col min="13" max="13" width="44.83203125" customWidth="1"/>
-    <col min="14" max="14" width="16.83203125" customWidth="1"/>
-    <col min="15" max="15" width="19.83203125" customWidth="1"/>
-    <col min="16" max="16" width="15.83203125" customWidth="1"/>
-    <col min="17" max="17" width="18.83203125" customWidth="1"/>
-    <col min="18" max="18" width="19.83203125" customWidth="1"/>
-    <col min="19" max="19" width="22.83203125" customWidth="1"/>
-    <col min="20" max="20" width="28.83203125" customWidth="1"/>
-    <col min="21" max="21" width="27.83203125" customWidth="1"/>
-    <col min="22" max="22" width="31.83203125" customWidth="1"/>
-    <col min="23" max="23" width="27.83203125" customWidth="1"/>
-    <col min="24" max="25" width="34.83203125" customWidth="1"/>
-    <col min="26" max="28" width="33.83203125" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="30" customHeight="1" x14ac:dyDescent="0.2"/>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <sheetData/>
+  <ignoredErrors>
+    <ignoredError numberStoredAsText="1" sqref="A1"/>
+  </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
-  <cols>
-    <col min="1" max="1" width="12.83203125" customWidth="1"/>
-    <col min="2" max="2" width="15.83203125" customWidth="1"/>
-    <col min="3" max="3" width="16.83203125" customWidth="1"/>
-    <col min="4" max="5" width="17.83203125" customWidth="1"/>
-    <col min="6" max="6" width="13.83203125" customWidth="1"/>
-    <col min="7" max="8" width="12.83203125" customWidth="1"/>
-    <col min="9" max="9" width="15.83203125" customWidth="1"/>
-    <col min="10" max="10" width="12.83203125" customWidth="1"/>
-    <col min="11" max="11" width="14.83203125" customWidth="1"/>
-    <col min="12" max="13" width="12.83203125" customWidth="1"/>
-    <col min="14" max="14" width="17.83203125" customWidth="1"/>
-    <col min="15" max="15" width="13.83203125" customWidth="1"/>
-    <col min="16" max="16" width="24.83203125" customWidth="1"/>
-    <col min="17" max="17" width="12.83203125" customWidth="1"/>
-    <col min="18" max="18" width="30.83203125" customWidth="1"/>
-    <col min="19" max="19" width="33.83203125" customWidth="1"/>
-    <col min="20" max="20" width="22.83203125" customWidth="1"/>
-    <col min="21" max="21" width="25.83203125" customWidth="1"/>
-    <col min="22" max="22" width="15.83203125" customWidth="1"/>
-    <col min="23" max="23" width="18.83203125" customWidth="1"/>
-    <col min="24" max="24" width="15.83203125" customWidth="1"/>
-    <col min="25" max="25" width="28.83203125" customWidth="1"/>
-    <col min="26" max="28" width="27.83203125" customWidth="1"/>
-    <col min="29" max="29" width="34.83203125" customWidth="1"/>
-    <col min="30" max="30" width="42.83203125" customWidth="1"/>
-    <col min="31" max="32" width="35.83203125" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="30" customHeight="1" x14ac:dyDescent="0.2"/>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <sheetData/>
+  <ignoredErrors>
+    <ignoredError numberStoredAsText="1" sqref="A1"/>
+  </ignoredErrors>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1"/>
+  <sheetData/>
+  <ignoredErrors>
+    <ignoredError numberStoredAsText="1" sqref="A1"/>
+  </ignoredErrors>
 </worksheet>
 </file>